--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487972_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487972_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2737</v>
+        <v>6.5607</v>
       </c>
       <c r="E2" t="n">
-        <v>7.09</v>
+        <v>7.1524</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8163</v>
+        <v>-0.5917</v>
       </c>
       <c r="G2" t="n">
         <v>4.9618</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9244</v>
+        <v>1.2114</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6647</v>
+        <v>0.727</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2597</v>
+        <v>0.4844</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6036</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2297</v>
+        <v>2.3314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8236</v>
+        <v>-0.4358</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4061</v>
+        <v>2.7672</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6339</v>
+        <v>1.4856</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.4006</v>
+        <v>0.3912</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2333</v>
+        <v>1.0944</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3869</v>
+        <v>0.1156</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4024</v>
+        <v>0.1078</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0156</v>
+        <v>0.0078</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.247</v>
+        <v>1.37</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9981</v>
+        <v>0.2834</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2488</v>
+        <v>1.0866</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3787</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1716</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8041</v>
+        <v>0.4671</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4525</v>
+        <v>0.4397</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3517</v>
+        <v>0.0274</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2666</v>
+        <v>-1.2071</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8701</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6317</v>
+        <v>0.7127</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7814</v>
+        <v>2.0684</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1497</v>
+        <v>-1.3556</v>
       </c>
       <c r="G4" t="n">
         <v>0.4045</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9606</v>
+        <v>1.0416</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2886</v>
+        <v>0.5755</v>
       </c>
       <c r="U4" t="n">
-        <v>0.672</v>
+        <v>0.4661</v>
       </c>
       <c r="V4" t="n">
         <v>-0.337</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4789</v>
+        <v>0.3886</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0076</v>
+        <v>-0.5402</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4864</v>
+        <v>0.9288</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4856</v>
+        <v>-2.6339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3912</v>
+        <v>-2.4006</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0944</v>
+        <v>-0.2333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1156</v>
+        <v>-0.3869</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1078</v>
+        <v>-0.4024</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0078</v>
+        <v>0.0156</v>
       </c>
       <c r="M5" t="n">
-        <v>1.37</v>
+        <v>-2.247</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2834</v>
+        <v>-1.9981</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0866</v>
+        <v>-0.2488</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-2.3787</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5769</v>
+        <v>3.1716</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3854</v>
+        <v>1.963</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.132</v>
+        <v>1.0887</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2534</v>
+        <v>0.8743</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0305</v>
+        <v>-0.911</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6268</v>
+        <v>-1.423</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.5121</v>
       </c>
       <c r="G6" t="n">
         <v>0.7702</v>
@@ -922,13 +922,13 @@
         <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3182</v>
+        <v>0.4377</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0552</v>
+        <v>0.2589</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2631</v>
+        <v>0.1788</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5331</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4323</v>
+        <v>-1.8927</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6636</v>
+        <v>-2.3767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2314</v>
+        <v>0.4841</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1287</v>
@@ -1000,13 +1000,13 @@
         <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5577</v>
+        <v>0.0973</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7967</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.239</v>
+        <v>0.0137</v>
       </c>
       <c r="V7" t="n">
         <v>0.337</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6515</v>
+        <v>-3.533</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0317</v>
+        <v>0.0941</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.6832</v>
+        <v>-3.6271</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5018</v>
@@ -1078,13 +1078,13 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0485</v>
+        <v>0.167</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1176</v>
+        <v>0.18</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0129</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8107</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9172</v>
+        <v>-3.9622</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.040900000000001</v>
+        <v>-6.5524</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1237</v>
+        <v>2.5902</v>
       </c>
       <c r="G9" t="n">
         <v>-3.145</v>
@@ -1156,13 +1156,13 @@
         <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1287</v>
+        <v>1.0838</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1855</v>
+        <v>0.303</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3142</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0.4778</v>
@@ -1189,19 +1189,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5824999999999996</v>
+        <v>-0.3055000000000003</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6122</v>
+        <v>-2.013199999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1947</v>
+        <v>1.708</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7873000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.0821</v>
+        <v>-7.082099999999999</v>
       </c>
       <c r="I10" t="n">
         <v>6.295000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>16.2543</v>
       </c>
       <c r="S10" t="n">
-        <v>7.3568</v>
+        <v>6.4689</v>
       </c>
       <c r="T10" t="n">
-        <v>4.057799999999999</v>
+        <v>3.6564</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2992</v>
+        <v>2.8125</v>
       </c>
       <c r="V10" t="n">
         <v>-3.4101</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.5436</v>
+        <v>3.6246</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5532</v>
+        <v>2.8588</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.7658</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3589</v>
@@ -1312,13 +1312,13 @@
         <v>3.3698</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2584</v>
+        <v>-1.1774</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0056</v>
+        <v>-0.7</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2528</v>
+        <v>-0.4775</v>
       </c>
       <c r="V11" t="n">
         <v>4.584</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.0194</v>
+        <v>2.9633</v>
       </c>
       <c r="E12" t="n">
         <v>2.4662</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5532</v>
+        <v>0.4971</v>
       </c>
       <c r="G12" t="n">
         <v>7.5089</v>
@@ -1390,13 +1390,13 @@
         <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5205</v>
+        <v>-1.5767</v>
       </c>
       <c r="T12" t="n">
         <v>-0.756</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7645</v>
+        <v>-0.8206</v>
       </c>
       <c r="V12" t="n">
         <v>-1.185</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2053</v>
+        <v>2.2542</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1418</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0635</v>
+        <v>1.3162</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9538</v>
@@ -1468,13 +1468,13 @@
         <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.874</v>
+        <v>-0.825</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0769</v>
+        <v>-0.2806</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7971</v>
+        <v>-0.5444</v>
       </c>
       <c r="V13" t="n">
         <v>3.4473</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2325</v>
+        <v>0.1895</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4428</v>
+        <v>0.3935</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2102</v>
+        <v>-0.204</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3504</v>
+        <v>0.2375</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9833</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3336</v>
+        <v>-0.3043</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0025</v>
+        <v>1.2039</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5611</v>
+        <v>1.8027</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5586</v>
+        <v>-0.5988</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3529</v>
+        <v>-0.9665</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5779</v>
+        <v>-1.2609</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.775</v>
+        <v>0.2945</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5858</v>
+        <v>-2.7751</v>
       </c>
       <c r="R15" t="n">
         <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.468</v>
+        <v>-1.0811</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4775</v>
+        <v>-0.4495</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9454</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6036</v>
+        <v>1.0331</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.337</v>
+        <v>2.4142</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2666</v>
+        <v>-1.3811</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4205</v>
+        <v>-0.6209</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3195</v>
+        <v>-0.1898</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.74</v>
+        <v>-0.4311</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1961</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0115</v>
+        <v>-0.189</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4847</v>
+        <v>-0.0246</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4732</v>
+        <v>-0.1644</v>
       </c>
       <c r="V16" t="n">
         <v>-2.218</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4217</v>
+        <v>-0.8052</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2177</v>
+        <v>-1.1558</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.204</v>
+        <v>0.3506</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2375</v>
+        <v>-0.3504</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.9833</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3043</v>
+        <v>-1.3336</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2039</v>
+        <v>1.0025</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8027</v>
+        <v>1.5611</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5988</v>
+        <v>-0.5586</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9665</v>
+        <v>-1.3529</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2609</v>
+        <v>-0.5779</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2945</v>
+        <v>-0.775</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7751</v>
+        <v>-1.5858</v>
       </c>
       <c r="R17" t="n">
         <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6923</v>
+        <v>-1.0407</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0608</v>
+        <v>-0.2356</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.805</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0331</v>
+        <v>-0.6036</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4142</v>
+        <v>-0.337</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3811</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9091</v>
+        <v>-0.8248</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1243</v>
+        <v>0.2085</v>
       </c>
       <c r="G18" t="n">
         <v>0.0259</v>
@@ -1858,13 +1858,13 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1421</v>
+        <v>-0.0578</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.165</v>
+        <v>-1.242</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1692</v>
+        <v>-0.9654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0042</v>
+        <v>-0.2766</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0606</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4992</v>
+        <v>0.4221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7488</v>
+        <v>0.468</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0867</v>
+        <v>-3.2552</v>
       </c>
       <c r="E20" t="n">
         <v>-4.7102</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6235</v>
+        <v>1.455</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3835</v>
@@ -2014,13 +2014,13 @@
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7943</v>
+        <v>0.6259</v>
       </c>
       <c r="T20" t="n">
         <v>0.2423</v>
       </c>
       <c r="U20" t="n">
-        <v>0.552</v>
+        <v>0.3835</v>
       </c>
       <c r="V20" t="n">
         <v>0.674</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6443</v>
+        <v>-3.3948</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3756</v>
+        <v>-2.07</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2687</v>
+        <v>-1.3248</v>
       </c>
       <c r="G21" t="n">
         <v>0.3872</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7276</v>
+        <v>-0.4781</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5616</v>
+        <v>-0.256</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.166</v>
+        <v>-0.2222</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7181</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5062000000000006</v>
+        <v>-0.5060000000000016</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8628</v>
+        <v>-2.862700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3566</v>
+        <v>2.3567</v>
       </c>
       <c r="G22" t="n">
         <v>1.461499999999999</v>
@@ -2152,7 +2152,7 @@
         <v>-2.1515</v>
       </c>
       <c r="M22" t="n">
-        <v>-9.3848</v>
+        <v>-9.384800000000002</v>
       </c>
       <c r="N22" t="n">
         <v>-4.8875</v>
@@ -2170,13 +2170,13 @@
         <v>18.8311</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.3779</v>
+        <v>-5.377800000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.5684</v>
+        <v>-2.5683</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8095</v>
+        <v>-2.8096</v>
       </c>
       <c r="V22" t="n">
         <v>3.4101</v>
